--- a/out/08_ISMS/SNX-ISMS-REG-02 IS Risk Assessment Register (Rev00 DRAFT).xlsx
+++ b/out/08_ISMS/SNX-ISMS-REG-02 IS Risk Assessment Register (Rev00 DRAFT).xlsx
@@ -15,7 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register Risiko'!$A$4:$Q$79</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Register Risiko'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Ringkasan'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -206,7 +209,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -414,6 +417,45 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -838,8 +880,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="A4" s="39" t="inlineStr">
+    <row r="3" s="36">
+      <c r="A3" s="70" t="n"/>
+      <c r="B3" s="70" t="n"/>
+      <c r="C3" s="70" t="n"/>
+      <c r="D3" s="70" t="n"/>
+      <c r="E3" s="70" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="36">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -849,9 +898,12 @@
           <t>SNX-ISMS-REG-02</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="C4" s="70" t="n"/>
+      <c r="D4" s="70" t="n"/>
+      <c r="E4" s="70" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="36">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -861,9 +913,12 @@
           <t>Information Security Risk Assessment Register</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="C5" s="70" t="n"/>
+      <c r="D5" s="70" t="n"/>
+      <c r="E5" s="70" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="36">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -873,9 +928,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="C6" s="70" t="n"/>
+      <c r="D6" s="70" t="n"/>
+      <c r="E6" s="70" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="36">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -885,9 +943,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="C7" s="70" t="n"/>
+      <c r="D7" s="70" t="n"/>
+      <c r="E7" s="70" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="36">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -897,9 +958,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="70" t="n"/>
+      <c r="E8" s="70" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="36">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -909,9 +973,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="C9" s="70" t="n"/>
+      <c r="D9" s="70" t="n"/>
+      <c r="E9" s="70" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="36">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -921,9 +988,12 @@
           <t>ISMS Coordinator</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="36">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="C10" s="70" t="n"/>
+      <c r="D10" s="70" t="n"/>
+      <c r="E10" s="70" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="36">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -933,9 +1003,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="36">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="C11" s="70" t="n"/>
+      <c r="D11" s="70" t="n"/>
+      <c r="E11" s="70" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="36">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -945,9 +1018,12 @@
           <t>Klausul 6.1</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="36">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="C12" s="70" t="n"/>
+      <c r="D12" s="70" t="n"/>
+      <c r="E12" s="70" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="36">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -957,9 +1033,12 @@
           <t>Klausul 6.1.2, 8.2</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="36">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="C13" s="70" t="n"/>
+      <c r="D13" s="70" t="n"/>
+      <c r="E13" s="70" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="36">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -969,152 +1048,215 @@
           <t>Berlaku sampai digantikan</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="36">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="C14" s="70" t="n"/>
+      <c r="D14" s="70" t="n"/>
+      <c r="E14" s="70" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="36">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="40" t="inlineStr">
         <is>
-          <t>Register penilaian risiko keamanan informasi (ISO/IEC 27001:2022 klausul 6.1.2 dan 8.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="36">
-      <c r="A17" s="41" t="inlineStr">
+          <t>Mencatat penilaian risiko keamanan informasi sesuai ISO/IEC 27001:2022 klausul 6.1.2 dan 8.2.</t>
+        </is>
+      </c>
+      <c r="C15" s="70" t="n"/>
+      <c r="D15" s="70" t="n"/>
+      <c r="E15" s="70" t="n"/>
+    </row>
+    <row r="16" s="36">
+      <c r="A16" s="70" t="n"/>
+      <c r="B16" s="70" t="n"/>
+      <c r="C16" s="70" t="n"/>
+      <c r="D16" s="70" t="n"/>
+      <c r="E16" s="70" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="36">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="23.85" customHeight="1" s="36">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="B17" s="70" t="n"/>
+      <c r="C17" s="70" t="n"/>
+      <c r="D17" s="70" t="n"/>
+      <c r="E17" s="70" t="n"/>
+    </row>
+    <row r="18" ht="43.5" customHeight="1" s="36">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="43" t="inlineStr">
         <is>
-          <t>Identifikasi risiko per aset atau kelompok aset (rujuk ID SNX-ISMS-REG-01): threat, vulnerability, dan dampak terhadap C, I, A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="36">
-      <c r="A19" s="42" t="inlineStr">
+          <t>Identifikasi risiko per aset atau kelompok aset, dengan ID aset dari SNX-ISMS-REG-01. Tulis threat, vulnerability, dan dampaknya terhadap C, I, A.</t>
+        </is>
+      </c>
+      <c r="C18" s="70" t="n"/>
+      <c r="D18" s="70" t="n"/>
+      <c r="E18" s="70" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="36">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="43" t="inlineStr">
         <is>
-          <t>Nilai Likelihood dan Impact 1 sampai 5 sesuai sheet Matriks Risiko; skor dan level dihitung otomatis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="36">
-      <c r="A20" s="42" t="inlineStr">
+          <t>Isi Likelihood (L) dan Impact (I) dengan nilai 1 sampai 5 sesuai sheet Matriks Risiko. Skor dan Level terisi otomatis.</t>
+        </is>
+      </c>
+      <c r="C19" s="70" t="n"/>
+      <c r="D19" s="70" t="n"/>
+      <c r="E19" s="70" t="n"/>
+    </row>
+    <row r="20" ht="43.5" customHeight="1" s="36">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="43" t="inlineStr">
         <is>
-          <t>Kriteria penerimaan: level Rendah dapat diterima pemilik risiko; Sedang ke atas wajib rencana penanganan di SNX-ISMS-REG-03.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="36">
-      <c r="A21" s="42" t="inlineStr">
+          <t>Kriteria penerimaan: risiko berlevel Rendah dapat diterima pemilik risiko. Risiko berlevel Sedang ke atas wajib memiliki rencana penanganan di SNX-ISMS-REG-03.</t>
+        </is>
+      </c>
+      <c r="C20" s="70" t="n"/>
+      <c r="D20" s="70" t="n"/>
+      <c r="E20" s="70" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="36">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="43" t="inlineStr">
         <is>
-          <t>Penilaian ulang minimal tahunan, setelah insiden P1, dan setelah perubahan besar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="23.85" customHeight="1" s="36">
-      <c r="A22" s="42" t="inlineStr">
+          <t>Lakukan penilaian ulang paling sedikit setahun sekali, setelah insiden P1, dan setelah perubahan besar.</t>
+        </is>
+      </c>
+      <c r="C21" s="70" t="n"/>
+      <c r="D21" s="70" t="n"/>
+      <c r="E21" s="70" t="n"/>
+    </row>
+    <row r="22" ht="43.5" customHeight="1" s="36">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>Usulan awal Divisi Operation dari riwayat operasi di knowledge base SINUX; wajib divalidasi ISMS Coordinator dan pemilik risiko.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="36">
-      <c r="A24" s="41" t="inlineStr">
+          <t>Baris usulan awal disusun Divisi Operation dari riwayat operasi di knowledge base SINUX. Baris tersebut wajib divalidasi ISMS Coordinator dan pemilik risiko.</t>
+        </is>
+      </c>
+      <c r="C22" s="70" t="n"/>
+      <c r="D22" s="70" t="n"/>
+      <c r="E22" s="70" t="n"/>
+    </row>
+    <row r="23" s="36">
+      <c r="A23" s="70" t="n"/>
+      <c r="B23" s="70" t="n"/>
+      <c r="C23" s="70" t="n"/>
+      <c r="D23" s="70" t="n"/>
+      <c r="E23" s="70" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="36">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="36">
-      <c r="A25" s="44" t="n"/>
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B24" s="70" t="n"/>
+      <c r="C24" s="70" t="n"/>
+      <c r="D24" s="70" t="n"/>
+      <c r="E24" s="70" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="36">
+      <c r="A25" s="73" t="n"/>
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="36">
-      <c r="A26" s="45" t="n"/>
-      <c r="B26" s="42" t="inlineStr">
+      <c r="C25" s="70" t="n"/>
+      <c r="D25" s="70" t="n"/>
+      <c r="E25" s="70" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1" s="36">
+      <c r="A26" s="74" t="n"/>
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>Biru muda: usulan awal Divisi Operation, belum berstatus Disetujui</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="36">
-      <c r="A27" s="46" t="n"/>
-      <c r="B27" s="42" t="inlineStr">
+      <c r="C26" s="70" t="n"/>
+      <c r="D26" s="70" t="n"/>
+      <c r="E26" s="70" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="36">
+      <c r="A27" s="75" t="n"/>
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="36">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="C27" s="70" t="n"/>
+      <c r="D27" s="70" t="n"/>
+      <c r="E27" s="70" t="n"/>
+    </row>
+    <row r="28" s="36">
+      <c r="A28" s="70" t="n"/>
+      <c r="B28" s="70" t="n"/>
+      <c r="C28" s="70" t="n"/>
+      <c r="D28" s="70" t="n"/>
+      <c r="E28" s="70" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="36">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="36">
-      <c r="A30" s="47" t="inlineStr">
+      <c r="B29" s="70" t="n"/>
+      <c r="C29" s="70" t="n"/>
+      <c r="D29" s="70" t="n"/>
+      <c r="E29" s="70" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="36">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B30" s="47" t="inlineStr">
+      <c r="B30" s="51" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C30" s="51" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D30" s="47" t="inlineStr">
+      <c r="D30" s="51" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E30" s="47" t="inlineStr">
+      <c r="E30" s="51" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1" s="36">
+    <row r="31" ht="30" customHeight="1" s="36">
       <c r="A31" s="40" t="inlineStr">
         <is>
           <t>00</t>
@@ -1148,76 +1290,91 @@
       <c r="D32" s="40" t="n"/>
       <c r="E32" s="40" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="36">
-      <c r="A34" s="41" t="inlineStr">
+    <row r="33" s="36">
+      <c r="A33" s="70" t="n"/>
+      <c r="B33" s="70" t="n"/>
+      <c r="C33" s="70" t="n"/>
+      <c r="D33" s="70" t="n"/>
+      <c r="E33" s="70" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="36">
+      <c r="A34" s="72" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="36">
-      <c r="A35" s="47" t="inlineStr">
+      <c r="B34" s="70" t="n"/>
+      <c r="C34" s="70" t="n"/>
+      <c r="D34" s="70" t="n"/>
+      <c r="E34" s="70" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="36">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B35" s="47" t="inlineStr">
+      <c r="B35" s="51" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C35" s="51" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D35" s="47" t="inlineStr">
+      <c r="D35" s="51" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E35" s="70" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="36">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B36" s="48" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C36" s="48" t="n"/>
-      <c r="D36" s="48" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="70" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="36">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B37" s="48" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C37" s="48" t="n"/>
-      <c r="D37" s="48" t="n"/>
+      <c r="C37" s="40" t="n"/>
+      <c r="D37" s="40" t="n"/>
+      <c r="E37" s="70" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="36">
-      <c r="A38" s="48" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B38" s="48" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C38" s="48" t="n"/>
-      <c r="D38" s="48" t="n"/>
+      <c r="C38" s="40" t="n"/>
+      <c r="D38" s="40" t="n"/>
+      <c r="E38" s="70" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1261,110 +1418,117 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="35" min="1" max="3"/>
+    <col width="14" customWidth="1" style="36" min="2" max="2"/>
+    <col width="13" customWidth="1" style="36" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="36">
-      <c r="A1" s="50" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="36">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>Skala</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="76" t="inlineStr">
         <is>
           <t>Keputusan</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="76" t="inlineStr">
         <is>
           <t>CIA</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="36">
-      <c r="A2" s="42" t="n">
+    <row r="2" ht="16.5" customHeight="1" s="36">
+      <c r="A2" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="42" t="inlineStr">
+      <c r="B2" s="77" t="inlineStr">
         <is>
           <t>Mitigasi</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="77" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="36">
-      <c r="A3" s="42" t="n">
+    <row r="3" ht="16.5" customHeight="1" s="36">
+      <c r="A3" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="77" t="inlineStr">
         <is>
           <t>Hindari</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="77" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="A4" s="42" t="n">
+    <row r="4" ht="16.5" customHeight="1" s="36">
+      <c r="A4" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="A5" s="42" t="n">
+    <row r="5" ht="16.5" customHeight="1" s="36">
+      <c r="A5" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>Terima</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="77" t="inlineStr">
         <is>
           <t>C, I</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="A6" s="42" t="n">
+    <row r="6" ht="16.5" customHeight="1" s="36">
+      <c r="A6" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="B6" s="78" t="n"/>
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>C, A</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="C7" s="42" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="36">
+      <c r="A7" s="78" t="n"/>
+      <c r="B7" s="78" t="n"/>
+      <c r="C7" s="77" t="inlineStr">
         <is>
           <t>I, A</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="C8" s="42" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="36">
+      <c r="A8" s="78" t="n"/>
+      <c r="B8" s="78" t="n"/>
+      <c r="C8" s="77" t="inlineStr">
         <is>
           <t>C, I, A</t>
         </is>
@@ -1373,7 +1537,7 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1386,20 +1550,22 @@
   <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9" customWidth="1" style="35" min="1" max="1"/>
+    <col width="10" customWidth="1" style="35" min="1" max="1"/>
     <col width="24" customWidth="1" style="35" min="2" max="2"/>
     <col width="22" customWidth="1" style="35" min="3" max="3"/>
     <col width="32" customWidth="1" style="35" min="4" max="4"/>
     <col width="7" customWidth="1" style="35" min="5" max="5"/>
     <col width="26" customWidth="1" style="35" min="6" max="6"/>
     <col width="4" customWidth="1" style="35" min="7" max="8"/>
-    <col width="6" customWidth="1" style="35" min="9" max="9"/>
+    <col width="13" customWidth="1" style="36" min="8" max="8"/>
+    <col width="7" customWidth="1" style="35" min="9" max="9"/>
     <col width="9" customWidth="1" style="35" min="10" max="10"/>
     <col width="16" customWidth="1" style="35" min="11" max="11"/>
     <col width="14" customWidth="1" style="35" min="12" max="12"/>
-    <col width="10" customWidth="1" style="35" min="13" max="13"/>
+    <col width="14" customWidth="1" style="35" min="13" max="13"/>
     <col width="9" customWidth="1" style="35" min="14" max="14"/>
-    <col width="11" customWidth="1" style="35" min="15" max="16"/>
+    <col width="14" customWidth="1" style="35" min="15" max="16"/>
+    <col width="14" customWidth="1" style="36" min="16" max="16"/>
     <col width="14" customWidth="1" style="35" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -1413,7 +1579,7 @@
     <row r="2" ht="15" customHeight="1" s="36">
       <c r="A2" s="38" t="inlineStr">
         <is>
-          <t>Baris biru muda = usulan awal: validasi lalu ubah kolom Catatan menjadi Disetujui.</t>
+          <t>Baris biru muda adalah usulan awal. Setelah divalidasi, ubah kolom Catatan menjadi Disetujui.</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1670,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="35.05" customHeight="1" s="36">
+    <row r="5" ht="57" customHeight="1" s="36">
       <c r="A5" s="52" t="inlineStr">
         <is>
           <t>ISR-001</t>
@@ -1582,7 +1748,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="35.05" customHeight="1" s="36">
+    <row r="6" ht="57" customHeight="1" s="36">
       <c r="A6" s="52" t="inlineStr">
         <is>
           <t>ISR-002</t>
@@ -1660,7 +1826,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="23.85" customHeight="1" s="36">
+    <row r="7" ht="30" customHeight="1" s="36">
       <c r="A7" s="52" t="inlineStr">
         <is>
           <t>ISR-003</t>
@@ -1738,7 +1904,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="35.05" customHeight="1" s="36">
+    <row r="8" ht="57" customHeight="1" s="36">
       <c r="A8" s="52" t="inlineStr">
         <is>
           <t>ISR-004</t>
@@ -1816,7 +1982,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="35.05" customHeight="1" s="36">
+    <row r="9" ht="43.5" customHeight="1" s="36">
       <c r="A9" s="52" t="inlineStr">
         <is>
           <t>ISR-005</t>
@@ -1894,7 +2060,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="23.85" customHeight="1" s="36">
+    <row r="10" ht="30" customHeight="1" s="36">
       <c r="A10" s="52" t="inlineStr">
         <is>
           <t>ISR-006</t>
@@ -1972,7 +2138,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="35.05" customHeight="1" s="36">
+    <row r="11" ht="57" customHeight="1" s="36">
       <c r="A11" s="52" t="inlineStr">
         <is>
           <t>ISR-007</t>
@@ -2050,7 +2216,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="23.85" customHeight="1" s="36">
+    <row r="12" ht="43.5" customHeight="1" s="36">
       <c r="A12" s="52" t="inlineStr">
         <is>
           <t>ISR-008</t>
@@ -2128,7 +2294,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="35.05" customHeight="1" s="36">
+    <row r="13" ht="57" customHeight="1" s="36">
       <c r="A13" s="52" t="inlineStr">
         <is>
           <t>ISR-009</t>
@@ -2206,7 +2372,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="35.05" customHeight="1" s="36">
+    <row r="14" ht="57" customHeight="1" s="36">
       <c r="A14" s="52" t="inlineStr">
         <is>
           <t>ISR-010</t>
@@ -2284,7 +2450,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="35.05" customHeight="1" s="36">
+    <row r="15" ht="43.5" customHeight="1" s="36">
       <c r="A15" s="52" t="inlineStr">
         <is>
           <t>ISR-011</t>
@@ -2362,7 +2528,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="23.85" customHeight="1" s="36">
+    <row r="16" ht="43.5" customHeight="1" s="36">
       <c r="A16" s="52" t="inlineStr">
         <is>
           <t>ISR-012</t>
@@ -2440,7 +2606,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="23.85" customHeight="1" s="36">
+    <row r="17" ht="43.5" customHeight="1" s="36">
       <c r="A17" s="52" t="inlineStr">
         <is>
           <t>ISR-013</t>
@@ -2518,7 +2684,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="23.85" customHeight="1" s="36">
+    <row r="18" ht="43.5" customHeight="1" s="36">
       <c r="A18" s="52" t="inlineStr">
         <is>
           <t>ISR-014</t>
@@ -2596,7 +2762,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="23.85" customHeight="1" s="36">
+    <row r="19" ht="43.5" customHeight="1" s="36">
       <c r="A19" s="52" t="inlineStr">
         <is>
           <t>ISR-015</t>
@@ -4390,7 +4556,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -4398,15 +4564,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="35" min="1" max="1"/>
     <col width="45" customWidth="1" style="35" min="2" max="2"/>
-    <col width="55" customWidth="1" style="35" min="3" max="3"/>
-    <col width="12" customWidth="1" style="35" min="4" max="7"/>
+    <col width="24" customWidth="1" style="35" min="3" max="3"/>
+    <col width="24" customWidth="1" style="35" min="4" max="7"/>
+    <col width="24" customWidth="1" style="36" min="5" max="5"/>
+    <col width="24" customWidth="1" style="36" min="6" max="6"/>
+    <col width="24" customWidth="1" style="36" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="36">
@@ -4600,7 +4769,8 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="36">
+    <row r="12" s="36"/>
+    <row r="13" ht="16.5" customHeight="1" s="36">
       <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Skala</t>
@@ -4617,7 +4787,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="36">
+    <row r="14" ht="43.5" customHeight="1" s="36">
       <c r="A14" s="40" t="n">
         <v>1</v>
       </c>
@@ -4632,7 +4802,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="23.85" customHeight="1" s="36">
+    <row r="15" ht="57" customHeight="1" s="36">
       <c r="A15" s="40" t="n">
         <v>2</v>
       </c>
@@ -4647,7 +4817,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="23.85" customHeight="1" s="36">
+    <row r="16" ht="57" customHeight="1" s="36">
       <c r="A16" s="40" t="n">
         <v>3</v>
       </c>
@@ -4662,7 +4832,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="36">
+    <row r="17" ht="57" customHeight="1" s="36">
       <c r="A17" s="40" t="n">
         <v>4</v>
       </c>
@@ -4677,7 +4847,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="23.85" customHeight="1" s="36">
+    <row r="18" ht="84" customHeight="1" s="36">
       <c r="A18" s="40" t="n">
         <v>5</v>
       </c>
@@ -4692,7 +4862,8 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="36">
+    <row r="19" s="36"/>
+    <row r="20" ht="16.5" customHeight="1" s="36">
       <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Level</t>
@@ -4704,7 +4875,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="36">
+    <row r="21" ht="16.5" customHeight="1" s="36">
       <c r="A21" s="64" t="inlineStr">
         <is>
           <t>Rendah</t>
@@ -4716,7 +4887,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="23.85" customHeight="1" s="36">
+    <row r="22" ht="30" customHeight="1" s="36">
       <c r="A22" s="65" t="inlineStr">
         <is>
           <t>Sedang</t>
@@ -4728,7 +4899,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="35.05" customHeight="1" s="36">
+    <row r="23" ht="43.5" customHeight="1" s="36">
       <c r="A23" s="66" t="inlineStr">
         <is>
           <t>Tinggi</t>
@@ -4740,7 +4911,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="23.85" customHeight="1" s="36">
+    <row r="24" ht="43.5" customHeight="1" s="36">
       <c r="A24" s="67" t="inlineStr">
         <is>
           <t>Kritis</t>
@@ -4755,7 +4926,7 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -4763,7 +4934,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -4779,69 +4950,69 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="36">
-      <c r="A3" s="47" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="36">
+      <c r="A3" s="79" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B3" s="47" t="inlineStr">
+      <c r="B3" s="79" t="inlineStr">
         <is>
           <t>Jumlah risiko</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="A4" s="68" t="inlineStr">
+    <row r="4" ht="17.9" customHeight="1" s="36">
+      <c r="A4" s="80" t="inlineStr">
         <is>
           <t>Kritis</t>
         </is>
       </c>
-      <c r="B4" s="46">
+      <c r="B4" s="81">
         <f>COUNTIF('Register Risiko'!$J$5:$J$79,A4)</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="A5" s="68" t="inlineStr">
+    <row r="5" ht="17.9" customHeight="1" s="36">
+      <c r="A5" s="80" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="B5" s="46">
+      <c r="B5" s="81">
         <f>COUNTIF('Register Risiko'!$J$5:$J$79,A5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="A6" s="68" t="inlineStr">
+    <row r="6" ht="17.9" customHeight="1" s="36">
+      <c r="A6" s="80" t="inlineStr">
         <is>
           <t>Sedang</t>
         </is>
       </c>
-      <c r="B6" s="46">
+      <c r="B6" s="81">
         <f>COUNTIF('Register Risiko'!$J$5:$J$79,A6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="A7" s="68" t="inlineStr">
+    <row r="7" ht="17.9" customHeight="1" s="36">
+      <c r="A7" s="80" t="inlineStr">
         <is>
           <t>Rendah</t>
         </is>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="81">
         <f>COUNTIF('Register Risiko'!$J$5:$J$79,A7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="A8" s="69" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="36">
+      <c r="A8" s="82" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="69">
+      <c r="B8" s="82">
         <f>SUM(B4:B7)</f>
         <v/>
       </c>
@@ -4863,6 +5034,6 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>